--- a/URS_Certifications 16.06.25.xlsx
+++ b/URS_Certifications 16.06.25.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\сайт\сайт2\Сайт на практику\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28F7549A-894C-4638-B9B3-BAD0AA8CFF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5EC005A-D57A-4EC0-BC6A-0CA4DC04A193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="URS_Certifications (93)" sheetId="1" r:id="rId1"/>
+    <sheet name="URS_Certifications (94)" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6057" uniqueCount="721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6062" uniqueCount="721">
   <si>
     <t>Название компании</t>
   </si>
@@ -3043,10 +3043,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1352"/>
+  <dimension ref="A1:G1353"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="7" width="10.21875" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -28377,39 +28377,39 @@
         <v>7703097990</v>
       </c>
       <c r="D1226" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="E1226" t="s">
-        <v>67</v>
+        <v>424</v>
       </c>
       <c r="F1226" t="s">
         <v>11</v>
       </c>
       <c r="G1226" s="1">
-        <v>45960</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="1227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1227" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1227" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C1227">
-        <v>7451385726</v>
+        <v>7703097990</v>
       </c>
       <c r="D1227" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E1227" t="s">
-        <v>10</v>
+        <v>424</v>
       </c>
       <c r="F1227" t="s">
         <v>11</v>
       </c>
       <c r="G1227" s="1">
-        <v>46534</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="1228" spans="1:7" x14ac:dyDescent="0.3">
@@ -28423,39 +28423,39 @@
         <v>7451385726</v>
       </c>
       <c r="D1228" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E1228" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F1228" t="s">
         <v>11</v>
       </c>
       <c r="G1228" s="1">
-        <v>45800</v>
+        <v>46534</v>
       </c>
     </row>
     <row r="1229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1229" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B1229" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C1229">
-        <v>6371000295</v>
+        <v>7451385726</v>
       </c>
       <c r="D1229" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E1229" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F1229" t="s">
         <v>11</v>
       </c>
       <c r="G1229" s="1">
-        <v>46594</v>
+        <v>45800</v>
       </c>
     </row>
     <row r="1230" spans="1:7" x14ac:dyDescent="0.3">
@@ -28469,104 +28469,110 @@
         <v>6371000295</v>
       </c>
       <c r="D1230" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E1230" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F1230" t="s">
         <v>11</v>
       </c>
       <c r="G1230" s="1">
-        <v>45793</v>
+        <v>46594</v>
       </c>
     </row>
     <row r="1231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1231" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1231" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C1231">
-        <v>7805539408</v>
+        <v>6371000295</v>
       </c>
       <c r="D1231" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E1231" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="F1231" t="s">
         <v>11</v>
       </c>
       <c r="G1231" s="1">
-        <v>46519</v>
+        <v>45793</v>
       </c>
     </row>
     <row r="1232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1232" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B1232" t="s">
         <v>24</v>
       </c>
       <c r="C1232">
-        <v>1650371043</v>
+        <v>7805539408</v>
       </c>
       <c r="D1232" t="s">
         <v>9</v>
       </c>
       <c r="E1232" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="F1232" t="s">
         <v>11</v>
       </c>
       <c r="G1232" s="1">
-        <v>45911</v>
+        <v>46519</v>
       </c>
     </row>
     <row r="1233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1233" t="s">
-        <v>641</v>
+        <v>640</v>
+      </c>
+      <c r="B1233" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1233">
+        <v>1650371043</v>
+      </c>
+      <c r="D1233" t="s">
+        <v>9</v>
       </c>
       <c r="E1233" t="s">
         <v>10</v>
       </c>
       <c r="F1233" t="s">
-        <v>327</v>
+        <v>11</v>
       </c>
       <c r="G1233" s="1">
-        <v>46643</v>
+        <v>45911</v>
       </c>
     </row>
     <row r="1234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1234" t="s">
-        <v>642</v>
-      </c>
-      <c r="B1234" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1234">
-        <v>7722607816</v>
-      </c>
-      <c r="D1234" t="s">
-        <v>9</v>
+        <v>641</v>
       </c>
       <c r="E1234" t="s">
         <v>10</v>
       </c>
       <c r="F1234" t="s">
-        <v>11</v>
+        <v>327</v>
       </c>
       <c r="G1234" s="1">
-        <v>46171</v>
+        <v>46643</v>
       </c>
     </row>
     <row r="1235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1235" t="s">
-        <v>643</v>
+        <v>642</v>
+      </c>
+      <c r="B1235" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1235">
+        <v>7722607816</v>
       </c>
       <c r="D1235" t="s">
         <v>9</v>
@@ -28575,10 +28581,10 @@
         <v>10</v>
       </c>
       <c r="F1235" t="s">
-        <v>350</v>
+        <v>11</v>
       </c>
       <c r="G1235" s="1">
-        <v>46604</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="1236" spans="1:7" x14ac:dyDescent="0.3">
@@ -28589,41 +28595,44 @@
         <v>9</v>
       </c>
       <c r="E1236" t="s">
-        <v>352</v>
+        <v>10</v>
       </c>
       <c r="F1236" t="s">
         <v>350</v>
       </c>
       <c r="G1236" s="1">
-        <v>46644</v>
+        <v>46604</v>
       </c>
     </row>
     <row r="1237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1237" t="s">
-        <v>644</v>
+        <v>643</v>
+      </c>
+      <c r="D1237" t="s">
+        <v>9</v>
       </c>
       <c r="E1237" t="s">
-        <v>10</v>
+        <v>352</v>
       </c>
       <c r="F1237" t="s">
         <v>350</v>
       </c>
       <c r="G1237" s="1">
+        <v>46644</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1238" t="s">
+        <v>644</v>
+      </c>
+      <c r="E1238" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1238" t="s">
+        <v>350</v>
+      </c>
+      <c r="G1238" s="1">
         <v>46613</v>
-      </c>
-    </row>
-    <row r="1238" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D1238" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1238" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1238" t="s">
-        <v>408</v>
-      </c>
-      <c r="G1238" s="1">
-        <v>46640</v>
       </c>
     </row>
     <row r="1239" spans="1:7" x14ac:dyDescent="0.3">
@@ -28631,7 +28640,7 @@
         <v>9</v>
       </c>
       <c r="E1239" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F1239" t="s">
         <v>408</v>
@@ -28641,54 +28650,45 @@
       </c>
     </row>
     <row r="1240" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1240" t="s">
-        <v>645</v>
-      </c>
       <c r="D1240" t="s">
         <v>9</v>
       </c>
       <c r="E1240" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F1240" t="s">
-        <v>350</v>
+        <v>408</v>
       </c>
       <c r="G1240" s="1">
-        <v>46716</v>
+        <v>46640</v>
       </c>
     </row>
     <row r="1241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1241" t="s">
-        <v>646</v>
-      </c>
-      <c r="B1241" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1241">
-        <v>5049025534</v>
+        <v>645</v>
       </c>
       <c r="D1241" t="s">
         <v>9</v>
       </c>
       <c r="E1241" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="F1241" t="s">
-        <v>11</v>
+        <v>350</v>
       </c>
       <c r="G1241" s="1">
-        <v>46528</v>
+        <v>46716</v>
       </c>
     </row>
     <row r="1242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1242" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B1242" t="s">
         <v>24</v>
       </c>
       <c r="C1242">
-        <v>6382098652</v>
+        <v>5049025534</v>
       </c>
       <c r="D1242" t="s">
         <v>9</v>
@@ -28700,7 +28700,7 @@
         <v>11</v>
       </c>
       <c r="G1242" s="1">
-        <v>46575</v>
+        <v>46528</v>
       </c>
     </row>
     <row r="1243" spans="1:7" x14ac:dyDescent="0.3">
@@ -28714,56 +28714,56 @@
         <v>6382098652</v>
       </c>
       <c r="D1243" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E1243" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F1243" t="s">
         <v>11</v>
       </c>
       <c r="G1243" s="1">
-        <v>45842</v>
+        <v>46575</v>
       </c>
     </row>
     <row r="1244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1244" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B1244" t="s">
         <v>24</v>
       </c>
       <c r="C1244">
-        <v>7801223114</v>
+        <v>6382098652</v>
       </c>
       <c r="D1244" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E1244" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="F1244" t="s">
         <v>11</v>
       </c>
       <c r="G1244" s="1">
-        <v>46622</v>
+        <v>45842</v>
       </c>
     </row>
     <row r="1245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1245" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1245" t="s">
         <v>24</v>
       </c>
       <c r="C1245">
-        <v>7804691720</v>
+        <v>7801223114</v>
       </c>
       <c r="D1245" t="s">
         <v>9</v>
       </c>
       <c r="E1245" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="F1245" t="s">
         <v>11</v>
@@ -28774,13 +28774,13 @@
     </row>
     <row r="1246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1246" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B1246" t="s">
         <v>24</v>
       </c>
       <c r="C1246">
-        <v>3604011804</v>
+        <v>7804691720</v>
       </c>
       <c r="D1246" t="s">
         <v>9</v>
@@ -28792,7 +28792,7 @@
         <v>11</v>
       </c>
       <c r="G1246" s="1">
-        <v>46625</v>
+        <v>46622</v>
       </c>
     </row>
     <row r="1247" spans="1:7" x14ac:dyDescent="0.3">
@@ -28806,27 +28806,39 @@
         <v>3604011804</v>
       </c>
       <c r="D1247" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1247" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1247" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1247" s="1">
+        <v>46625</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1248" t="s">
+        <v>650</v>
+      </c>
+      <c r="B1248" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1248">
+        <v>3604011804</v>
+      </c>
+      <c r="D1248" t="s">
         <v>651</v>
       </c>
-      <c r="E1247" t="s">
+      <c r="E1248" t="s">
         <v>652</v>
       </c>
-      <c r="F1247" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1247" s="1">
+      <c r="F1248" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1248" s="1">
         <v>45379</v>
-      </c>
-    </row>
-    <row r="1248" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E1248" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1248" t="s">
-        <v>350</v>
-      </c>
-      <c r="G1248" s="1">
-        <v>46622</v>
       </c>
     </row>
     <row r="1249" spans="1:7" x14ac:dyDescent="0.3">
@@ -28834,56 +28846,44 @@
         <v>10</v>
       </c>
       <c r="F1249" t="s">
+        <v>350</v>
+      </c>
+      <c r="G1249" s="1">
+        <v>46622</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E1250" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1250" t="s">
         <v>653</v>
       </c>
-      <c r="G1249" s="1">
+      <c r="G1250" s="1">
         <v>46654</v>
-      </c>
-    </row>
-    <row r="1250" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1250" t="s">
-        <v>654</v>
-      </c>
-      <c r="B1250" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1250">
-        <v>7709788673</v>
-      </c>
-      <c r="D1250" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1250" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1250" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1250" s="1">
-        <v>46597</v>
       </c>
     </row>
     <row r="1251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1251" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B1251" t="s">
         <v>24</v>
       </c>
       <c r="C1251">
-        <v>7801399929</v>
+        <v>7709788673</v>
       </c>
       <c r="D1251" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E1251" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F1251" t="s">
         <v>11</v>
       </c>
       <c r="G1251" s="1">
-        <v>46793</v>
+        <v>46597</v>
       </c>
     </row>
     <row r="1252" spans="1:7" x14ac:dyDescent="0.3">
@@ -28897,16 +28897,16 @@
         <v>7801399929</v>
       </c>
       <c r="D1252" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="E1252" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F1252" t="s">
         <v>11</v>
       </c>
       <c r="G1252" s="1">
-        <v>46773</v>
+        <v>46793</v>
       </c>
     </row>
     <row r="1253" spans="1:7" x14ac:dyDescent="0.3">
@@ -28920,7 +28920,7 @@
         <v>7801399929</v>
       </c>
       <c r="D1253" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="E1253" t="s">
         <v>10</v>
@@ -28934,53 +28934,53 @@
     </row>
     <row r="1254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1254" t="s">
+        <v>655</v>
+      </c>
+      <c r="B1254" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1254">
+        <v>7801399929</v>
+      </c>
+      <c r="D1254" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1254" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1254" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1254" s="1">
+        <v>46773</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1255" t="s">
         <v>656</v>
       </c>
-      <c r="B1254" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1254" t="s">
+      <c r="B1255" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1255" t="s">
         <v>18</v>
       </c>
-      <c r="E1254" t="s">
+      <c r="E1255" t="s">
         <v>19</v>
       </c>
-      <c r="F1254" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1255" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E1255" t="s">
-        <v>10</v>
-      </c>
       <c r="F1255" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E1256" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1256" t="s">
         <v>653</v>
       </c>
-      <c r="G1255" s="1">
+      <c r="G1256" s="1">
         <v>45574</v>
-      </c>
-    </row>
-    <row r="1256" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1256" t="s">
-        <v>657</v>
-      </c>
-      <c r="B1256" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1256">
-        <v>1837004725</v>
-      </c>
-      <c r="D1256" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1256" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1256" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1256" s="1">
-        <v>46019</v>
       </c>
     </row>
     <row r="1257" spans="1:7" x14ac:dyDescent="0.3">
@@ -28997,47 +28997,47 @@
         <v>58</v>
       </c>
       <c r="E1257" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F1257" t="s">
         <v>11</v>
       </c>
       <c r="G1257" s="1">
-        <v>46017</v>
+        <v>46019</v>
       </c>
     </row>
     <row r="1258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1258" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1258" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C1258">
-        <v>7816145170</v>
+        <v>1837004725</v>
       </c>
       <c r="D1258" t="s">
         <v>58</v>
       </c>
       <c r="E1258" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F1258" t="s">
         <v>11</v>
       </c>
       <c r="G1258" s="1">
-        <v>46596</v>
+        <v>46017</v>
       </c>
     </row>
     <row r="1259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1259" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B1259" t="s">
         <v>8</v>
       </c>
       <c r="C1259">
-        <v>7814027653</v>
+        <v>7816145170</v>
       </c>
       <c r="D1259" t="s">
         <v>58</v>
@@ -29049,7 +29049,7 @@
         <v>11</v>
       </c>
       <c r="G1259" s="1">
-        <v>45939</v>
+        <v>46596</v>
       </c>
     </row>
     <row r="1260" spans="1:7" x14ac:dyDescent="0.3">
@@ -29063,16 +29063,16 @@
         <v>7814027653</v>
       </c>
       <c r="D1260" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="E1260" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F1260" t="s">
         <v>11</v>
       </c>
       <c r="G1260" s="1">
-        <v>45924</v>
+        <v>45939</v>
       </c>
     </row>
     <row r="1261" spans="1:7" x14ac:dyDescent="0.3">
@@ -29086,105 +29086,105 @@
         <v>7814027653</v>
       </c>
       <c r="D1261" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1261" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F1261" t="s">
         <v>11</v>
       </c>
       <c r="G1261" s="1">
-        <v>46710</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="1262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1262" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B1262" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C1262">
-        <v>6027207282</v>
+        <v>7814027653</v>
       </c>
       <c r="D1262" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E1262" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F1262" t="s">
         <v>11</v>
+      </c>
+      <c r="G1262" s="1">
+        <v>46710</v>
       </c>
     </row>
     <row r="1263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1263" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B1263" t="s">
         <v>24</v>
       </c>
       <c r="C1263">
-        <v>100070995</v>
+        <v>6027207282</v>
       </c>
       <c r="D1263" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1263" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F1263" t="s">
-        <v>88</v>
-      </c>
-      <c r="G1263" s="1">
-        <v>46729</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1264" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B1264" t="s">
-        <v>663</v>
-      </c>
-      <c r="C1264" s="2">
-        <v>632000000000</v>
+        <v>24</v>
+      </c>
+      <c r="C1264">
+        <v>100070995</v>
       </c>
       <c r="D1264" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="E1264" t="s">
         <v>10</v>
       </c>
       <c r="F1264" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="G1264" s="1">
-        <v>46730</v>
+        <v>46729</v>
       </c>
     </row>
     <row r="1265" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1265" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1265" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1265">
-        <v>4524000693</v>
+        <v>663</v>
+      </c>
+      <c r="C1265" s="2">
+        <v>632000000000</v>
       </c>
       <c r="D1265" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E1265" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F1265" t="s">
         <v>11</v>
       </c>
       <c r="G1265" s="1">
-        <v>45870</v>
+        <v>46730</v>
       </c>
     </row>
     <row r="1266" spans="1:7" x14ac:dyDescent="0.3">
@@ -29198,50 +29198,50 @@
         <v>4524000693</v>
       </c>
       <c r="D1266" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1266" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F1266" t="s">
         <v>11</v>
       </c>
       <c r="G1266" s="1">
-        <v>46717</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="1267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1267" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B1267" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C1267">
-        <v>7838510490</v>
+        <v>4524000693</v>
       </c>
       <c r="D1267" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E1267" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F1267" t="s">
         <v>11</v>
       </c>
       <c r="G1267" s="1">
-        <v>46575</v>
+        <v>46717</v>
       </c>
     </row>
     <row r="1268" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1268" t="s">
-        <v>500</v>
+        <v>665</v>
       </c>
       <c r="B1268" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C1268">
-        <v>1828007328</v>
+        <v>7838510490</v>
       </c>
       <c r="D1268" t="s">
         <v>20</v>
@@ -29252,36 +29252,36 @@
       <c r="F1268" t="s">
         <v>11</v>
       </c>
+      <c r="G1268" s="1">
+        <v>46575</v>
+      </c>
     </row>
     <row r="1269" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1269" t="s">
-        <v>666</v>
+        <v>500</v>
       </c>
       <c r="B1269" t="s">
-        <v>667</v>
+        <v>8</v>
+      </c>
+      <c r="C1269">
+        <v>1828007328</v>
       </c>
       <c r="D1269" t="s">
-        <v>651</v>
+        <v>20</v>
       </c>
       <c r="E1269" t="s">
-        <v>652</v>
+        <v>21</v>
       </c>
       <c r="F1269" t="s">
-        <v>668</v>
-      </c>
-      <c r="G1269" s="1">
-        <v>46377</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1270" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1270" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="B1270" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1270">
-        <v>3257017280</v>
+        <v>667</v>
       </c>
       <c r="D1270" t="s">
         <v>651</v>
@@ -29290,55 +29290,55 @@
         <v>652</v>
       </c>
       <c r="F1270" t="s">
-        <v>11</v>
+        <v>668</v>
+      </c>
+      <c r="G1270" s="1">
+        <v>46377</v>
       </c>
     </row>
     <row r="1271" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1271" t="s">
+        <v>669</v>
+      </c>
+      <c r="B1271" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1271">
+        <v>3257017280</v>
+      </c>
       <c r="D1271" t="s">
-        <v>9</v>
+        <v>651</v>
       </c>
       <c r="E1271" t="s">
-        <v>10</v>
+        <v>652</v>
       </c>
       <c r="F1271" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D1272" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1272" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1272" t="s">
         <v>653</v>
       </c>
-      <c r="G1271" s="1">
+      <c r="G1272" s="1">
         <v>46719</v>
-      </c>
-    </row>
-    <row r="1272" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1272" t="s">
-        <v>670</v>
-      </c>
-      <c r="B1272" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1272">
-        <v>5030090040</v>
-      </c>
-      <c r="D1272" t="s">
-        <v>651</v>
-      </c>
-      <c r="E1272" t="s">
-        <v>652</v>
-      </c>
-      <c r="F1272" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1272" s="1">
-        <v>46362</v>
       </c>
     </row>
     <row r="1273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1273" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1273" t="s">
         <v>24</v>
       </c>
       <c r="C1273">
-        <v>5834052005</v>
+        <v>5030090040</v>
       </c>
       <c r="D1273" t="s">
         <v>651</v>
@@ -29349,16 +29349,19 @@
       <c r="F1273" t="s">
         <v>11</v>
       </c>
+      <c r="G1273" s="1">
+        <v>46362</v>
+      </c>
     </row>
     <row r="1274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1274" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B1274" t="s">
         <v>24</v>
       </c>
       <c r="C1274">
-        <v>7733660353</v>
+        <v>5834052005</v>
       </c>
       <c r="D1274" t="s">
         <v>651</v>
@@ -29369,19 +29372,16 @@
       <c r="F1274" t="s">
         <v>11</v>
       </c>
-      <c r="G1274" s="1">
-        <v>46364</v>
-      </c>
     </row>
     <row r="1275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1275" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B1275" t="s">
         <v>24</v>
       </c>
       <c r="C1275">
-        <v>1644034949</v>
+        <v>7733660353</v>
       </c>
       <c r="D1275" t="s">
         <v>651</v>
@@ -29393,44 +29393,47 @@
         <v>11</v>
       </c>
       <c r="G1275" s="1">
-        <v>46467</v>
+        <v>46364</v>
       </c>
     </row>
     <row r="1276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1276" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B1276" t="s">
         <v>24</v>
       </c>
       <c r="C1276">
-        <v>8610024374</v>
+        <v>1644034949</v>
       </c>
       <c r="D1276" t="s">
         <v>651</v>
       </c>
       <c r="E1276" t="s">
-        <v>675</v>
+        <v>652</v>
       </c>
       <c r="F1276" t="s">
         <v>11</v>
+      </c>
+      <c r="G1276" s="1">
+        <v>46467</v>
       </c>
     </row>
     <row r="1277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1277" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B1277" t="s">
         <v>24</v>
       </c>
       <c r="C1277">
-        <v>5504168160</v>
+        <v>8610024374</v>
       </c>
       <c r="D1277" t="s">
         <v>651</v>
       </c>
       <c r="E1277" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="F1277" t="s">
         <v>11</v>
@@ -29438,59 +29441,56 @@
     </row>
     <row r="1278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1278" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B1278" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C1278">
-        <v>6317126596</v>
+        <v>5504168160</v>
       </c>
       <c r="D1278" t="s">
         <v>651</v>
       </c>
       <c r="E1278" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F1278" t="s">
         <v>11</v>
-      </c>
-      <c r="G1278" s="1">
-        <v>46692</v>
       </c>
     </row>
     <row r="1279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1279" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1279" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C1279">
-        <v>7017462729</v>
+        <v>6317126596</v>
       </c>
       <c r="D1279" t="s">
         <v>651</v>
       </c>
       <c r="E1279" t="s">
-        <v>652</v>
+        <v>675</v>
       </c>
       <c r="F1279" t="s">
         <v>11</v>
       </c>
       <c r="G1279" s="1">
-        <v>46502</v>
+        <v>46692</v>
       </c>
     </row>
     <row r="1280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1280" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B1280" t="s">
         <v>24</v>
       </c>
       <c r="C1280">
-        <v>7811438750</v>
+        <v>7017462729</v>
       </c>
       <c r="D1280" t="s">
         <v>651</v>
@@ -29502,12 +29502,12 @@
         <v>11</v>
       </c>
       <c r="G1280" s="1">
-        <v>46439</v>
+        <v>46502</v>
       </c>
     </row>
     <row r="1281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1281" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B1281" t="s">
         <v>24</v>
@@ -29516,16 +29516,16 @@
         <v>7811438750</v>
       </c>
       <c r="D1281" t="s">
-        <v>58</v>
+        <v>651</v>
       </c>
       <c r="E1281" t="s">
-        <v>10</v>
+        <v>652</v>
       </c>
       <c r="F1281" t="s">
         <v>11</v>
       </c>
       <c r="G1281" s="1">
-        <v>46837</v>
+        <v>46439</v>
       </c>
     </row>
     <row r="1282" spans="1:7" x14ac:dyDescent="0.3">
@@ -29539,7 +29539,7 @@
         <v>7811438750</v>
       </c>
       <c r="D1282" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="E1282" t="s">
         <v>10</v>
@@ -29553,141 +29553,141 @@
     </row>
     <row r="1283" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1283" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B1283" t="s">
         <v>24</v>
       </c>
       <c r="C1283">
-        <v>5505217893</v>
+        <v>7811438750</v>
       </c>
       <c r="D1283" t="s">
-        <v>651</v>
+        <v>14</v>
       </c>
       <c r="E1283" t="s">
-        <v>652</v>
+        <v>10</v>
       </c>
       <c r="F1283" t="s">
         <v>11</v>
       </c>
       <c r="G1283" s="1">
-        <v>46440</v>
+        <v>46837</v>
       </c>
     </row>
     <row r="1284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1284" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B1284" t="s">
         <v>24</v>
+      </c>
+      <c r="C1284">
+        <v>5505217893</v>
+      </c>
+      <c r="D1284" t="s">
+        <v>651</v>
+      </c>
+      <c r="E1284" t="s">
+        <v>652</v>
+      </c>
+      <c r="F1284" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1284" s="1">
+        <v>46440</v>
       </c>
     </row>
     <row r="1285" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1285" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1285" t="s">
-        <v>651</v>
-      </c>
-      <c r="C1285" t="s">
-        <v>675</v>
-      </c>
-      <c r="D1285" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1285" s="1">
-        <v>46677</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1286" t="s">
+        <v>684</v>
+      </c>
+      <c r="B1286" t="s">
+        <v>651</v>
+      </c>
+      <c r="C1286" t="s">
+        <v>675</v>
+      </c>
+      <c r="D1286" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1286" s="1">
+        <v>46677</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1287" t="s">
         <v>685</v>
       </c>
-      <c r="B1286" t="s">
+      <c r="B1287" t="s">
         <v>686</v>
       </c>
-      <c r="D1286" t="s">
+      <c r="D1287" t="s">
         <v>651</v>
       </c>
-      <c r="E1286" t="s">
+      <c r="E1287" t="s">
         <v>652</v>
       </c>
-      <c r="F1286" t="s">
+      <c r="F1287" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="1287" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D1287" t="s">
-        <v>687</v>
-      </c>
-      <c r="E1287" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1287" t="s">
-        <v>688</v>
-      </c>
-      <c r="G1287" s="1">
-        <v>46769</v>
       </c>
     </row>
     <row r="1288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D1288" t="s">
-        <v>9</v>
+        <v>687</v>
       </c>
       <c r="E1288" t="s">
         <v>10</v>
       </c>
       <c r="F1288" t="s">
+        <v>688</v>
+      </c>
+      <c r="G1288" s="1">
+        <v>46769</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D1289" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1289" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1289" t="s">
         <v>689</v>
       </c>
-      <c r="G1288" s="1">
+      <c r="G1289" s="1">
         <v>46766</v>
-      </c>
-    </row>
-    <row r="1289" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1289" t="s">
-        <v>690</v>
-      </c>
-      <c r="B1289" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1289">
-        <v>6321191904</v>
-      </c>
-      <c r="D1289" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1289" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1289" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1289" s="1">
-        <v>46760</v>
       </c>
     </row>
     <row r="1290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1290" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B1290" t="s">
         <v>24</v>
       </c>
       <c r="C1290">
-        <v>5837044394</v>
+        <v>6321191904</v>
       </c>
       <c r="D1290" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="E1290" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="F1290" t="s">
         <v>11</v>
       </c>
       <c r="G1290" s="1">
-        <v>46781</v>
+        <v>46760</v>
       </c>
     </row>
     <row r="1291" spans="1:7" x14ac:dyDescent="0.3">
@@ -29701,16 +29701,16 @@
         <v>5837044394</v>
       </c>
       <c r="D1291" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="E1291" t="s">
-        <v>299</v>
+        <v>51</v>
       </c>
       <c r="F1291" t="s">
         <v>11</v>
       </c>
       <c r="G1291" s="1">
-        <v>46822</v>
+        <v>46781</v>
       </c>
     </row>
     <row r="1292" spans="1:7" x14ac:dyDescent="0.3">
@@ -29724,7 +29724,7 @@
         <v>5837044394</v>
       </c>
       <c r="D1292" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E1292" t="s">
         <v>299</v>
@@ -29738,71 +29738,71 @@
     </row>
     <row r="1293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1293" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B1293" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C1293">
-        <v>5246058666</v>
+        <v>5837044394</v>
       </c>
       <c r="D1293" t="s">
         <v>14</v>
       </c>
       <c r="E1293" t="s">
-        <v>10</v>
+        <v>299</v>
       </c>
       <c r="F1293" t="s">
         <v>11</v>
       </c>
       <c r="G1293" s="1">
-        <v>46709</v>
+        <v>46822</v>
       </c>
     </row>
     <row r="1294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1294" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1294" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C1294">
-        <v>3801142563</v>
+        <v>5246058666</v>
       </c>
       <c r="D1294" t="s">
         <v>14</v>
       </c>
       <c r="E1294" t="s">
-        <v>352</v>
+        <v>10</v>
       </c>
       <c r="F1294" t="s">
         <v>11</v>
       </c>
       <c r="G1294" s="1">
-        <v>46736</v>
+        <v>46709</v>
       </c>
     </row>
     <row r="1295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1295" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B1295" t="s">
         <v>24</v>
       </c>
       <c r="C1295">
-        <v>1215117480</v>
+        <v>3801142563</v>
       </c>
       <c r="D1295" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="E1295" t="s">
-        <v>10</v>
+        <v>352</v>
       </c>
       <c r="F1295" t="s">
         <v>11</v>
       </c>
       <c r="G1295" s="1">
-        <v>46718</v>
+        <v>46736</v>
       </c>
     </row>
     <row r="1296" spans="1:7" x14ac:dyDescent="0.3">
@@ -29816,7 +29816,7 @@
         <v>1215117480</v>
       </c>
       <c r="D1296" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="E1296" t="s">
         <v>10</v>
@@ -29830,48 +29830,48 @@
     </row>
     <row r="1297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1297" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1297" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C1297">
-        <v>600009233</v>
+        <v>1215117480</v>
       </c>
       <c r="D1297" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E1297" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F1297" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="G1297" s="1">
-        <v>46597</v>
+        <v>46718</v>
       </c>
     </row>
     <row r="1298" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1298" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B1298" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C1298">
-        <v>6321231498</v>
+        <v>600009233</v>
       </c>
       <c r="D1298" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="E1298" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F1298" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="G1298" s="1">
-        <v>46731</v>
+        <v>46597</v>
       </c>
     </row>
     <row r="1299" spans="1:7" x14ac:dyDescent="0.3">
@@ -29885,59 +29885,59 @@
         <v>6321231498</v>
       </c>
       <c r="D1299" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E1299" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F1299" t="s">
         <v>11</v>
       </c>
       <c r="G1299" s="1">
-        <v>45975</v>
+        <v>46731</v>
       </c>
     </row>
     <row r="1300" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1300" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B1300" t="s">
         <v>24</v>
       </c>
       <c r="C1300">
-        <v>7705476338</v>
+        <v>6321231498</v>
       </c>
       <c r="D1300" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="E1300" t="s">
-        <v>424</v>
+        <v>13</v>
       </c>
       <c r="F1300" t="s">
         <v>11</v>
+      </c>
+      <c r="G1300" s="1">
+        <v>45975</v>
       </c>
     </row>
     <row r="1301" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1301" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1301" t="s">
         <v>24</v>
       </c>
       <c r="C1301">
-        <v>9703037297</v>
+        <v>7705476338</v>
       </c>
       <c r="D1301" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="E1301" t="s">
-        <v>10</v>
+        <v>424</v>
       </c>
       <c r="F1301" t="s">
         <v>11</v>
-      </c>
-      <c r="G1301" s="1">
-        <v>46729</v>
       </c>
     </row>
     <row r="1302" spans="1:7" x14ac:dyDescent="0.3">
@@ -29951,7 +29951,7 @@
         <v>9703037297</v>
       </c>
       <c r="D1302" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="E1302" t="s">
         <v>10</v>
@@ -29974,39 +29974,39 @@
         <v>9703037297</v>
       </c>
       <c r="D1303" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E1303" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F1303" t="s">
         <v>11</v>
       </c>
       <c r="G1303" s="1">
-        <v>46787</v>
+        <v>46729</v>
       </c>
     </row>
     <row r="1304" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1304" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B1304" t="s">
         <v>24</v>
       </c>
       <c r="C1304">
-        <v>6415003465</v>
+        <v>9703037297</v>
       </c>
       <c r="D1304" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="E1304" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F1304" t="s">
         <v>11</v>
       </c>
       <c r="G1304" s="1">
-        <v>46744</v>
+        <v>46787</v>
       </c>
     </row>
     <row r="1305" spans="1:7" x14ac:dyDescent="0.3">
@@ -30020,10 +30020,10 @@
         <v>6415003465</v>
       </c>
       <c r="D1305" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E1305" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F1305" t="s">
         <v>11</v>
@@ -30043,10 +30043,10 @@
         <v>6415003465</v>
       </c>
       <c r="D1306" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E1306" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F1306" t="s">
         <v>11</v>
@@ -30069,7 +30069,7 @@
         <v>14</v>
       </c>
       <c r="E1307" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F1307" t="s">
         <v>11</v>
@@ -30080,16 +30080,16 @@
     </row>
     <row r="1308" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1308" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B1308" t="s">
         <v>24</v>
       </c>
       <c r="C1308">
-        <v>9703143707</v>
+        <v>6415003465</v>
       </c>
       <c r="D1308" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E1308" t="s">
         <v>19</v>
@@ -30097,28 +30097,28 @@
       <c r="F1308" t="s">
         <v>11</v>
       </c>
+      <c r="G1308" s="1">
+        <v>46744</v>
+      </c>
     </row>
     <row r="1309" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1309" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1309" t="s">
         <v>24</v>
       </c>
       <c r="C1309">
-        <v>7814069526</v>
+        <v>9703143707</v>
       </c>
       <c r="D1309" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E1309" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F1309" t="s">
         <v>11</v>
-      </c>
-      <c r="G1309" s="1">
-        <v>46066</v>
       </c>
     </row>
     <row r="1310" spans="1:7" x14ac:dyDescent="0.3">
@@ -30132,16 +30132,16 @@
         <v>7814069526</v>
       </c>
       <c r="D1310" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="E1310" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F1310" t="s">
         <v>11</v>
       </c>
       <c r="G1310" s="1">
-        <v>46849</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="1311" spans="1:7" x14ac:dyDescent="0.3">
@@ -30155,7 +30155,7 @@
         <v>7814069526</v>
       </c>
       <c r="D1311" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="E1311" t="s">
         <v>10</v>
@@ -30169,25 +30169,25 @@
     </row>
     <row r="1312" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1312" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B1312" t="s">
         <v>24</v>
       </c>
       <c r="C1312">
-        <v>7805276082</v>
+        <v>7814069526</v>
       </c>
       <c r="D1312" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1312" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F1312" t="s">
         <v>11</v>
       </c>
       <c r="G1312" s="1">
-        <v>46066</v>
+        <v>46849</v>
       </c>
     </row>
     <row r="1313" spans="1:7" x14ac:dyDescent="0.3">
@@ -30201,16 +30201,16 @@
         <v>7805276082</v>
       </c>
       <c r="D1313" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="E1313" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F1313" t="s">
         <v>11</v>
       </c>
       <c r="G1313" s="1">
-        <v>46846</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="1314" spans="1:7" x14ac:dyDescent="0.3">
@@ -30224,7 +30224,7 @@
         <v>7805276082</v>
       </c>
       <c r="D1314" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="E1314" t="s">
         <v>10</v>
@@ -30238,19 +30238,25 @@
     </row>
     <row r="1315" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1315" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1315" t="s">
         <v>24</v>
       </c>
       <c r="C1315">
-        <v>2462036622</v>
+        <v>7805276082</v>
+      </c>
+      <c r="D1315" t="s">
+        <v>14</v>
       </c>
       <c r="E1315" t="s">
         <v>10</v>
       </c>
       <c r="F1315" t="s">
         <v>11</v>
+      </c>
+      <c r="G1315" s="1">
+        <v>46846</v>
       </c>
     </row>
     <row r="1316" spans="1:7" x14ac:dyDescent="0.3">
@@ -30264,7 +30270,7 @@
         <v>2462036622</v>
       </c>
       <c r="E1316" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F1316" t="s">
         <v>11</v>
@@ -30272,25 +30278,19 @@
     </row>
     <row r="1317" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1317" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B1317" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C1317">
-        <v>7720906560</v>
-      </c>
-      <c r="D1317" t="s">
-        <v>80</v>
+        <v>2462036622</v>
       </c>
       <c r="E1317" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F1317" t="s">
         <v>11</v>
-      </c>
-      <c r="G1317" s="1">
-        <v>46806</v>
       </c>
     </row>
     <row r="1318" spans="1:7" x14ac:dyDescent="0.3">
@@ -30304,7 +30304,7 @@
         <v>7720906560</v>
       </c>
       <c r="D1318" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="E1318" t="s">
         <v>10</v>
@@ -30318,19 +30318,25 @@
     </row>
     <row r="1319" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1319" t="s">
-        <v>705</v>
+        <v>704</v>
+      </c>
+      <c r="B1319" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1319">
+        <v>7720906560</v>
       </c>
       <c r="D1319" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="E1319" t="s">
         <v>10</v>
       </c>
       <c r="F1319" t="s">
-        <v>408</v>
+        <v>11</v>
       </c>
       <c r="G1319" s="1">
-        <v>46788</v>
+        <v>46806</v>
       </c>
     </row>
     <row r="1320" spans="1:7" x14ac:dyDescent="0.3">
@@ -30341,13 +30347,13 @@
         <v>80</v>
       </c>
       <c r="E1320" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F1320" t="s">
         <v>408</v>
       </c>
       <c r="G1320" s="1">
-        <v>46787</v>
+        <v>46788</v>
       </c>
     </row>
     <row r="1321" spans="1:7" x14ac:dyDescent="0.3">
@@ -30358,7 +30364,7 @@
         <v>80</v>
       </c>
       <c r="E1321" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F1321" t="s">
         <v>408</v>
@@ -30369,30 +30375,33 @@
     </row>
     <row r="1322" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1322" t="s">
-        <v>706</v>
-      </c>
-      <c r="B1322" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1322">
-        <v>6661044752</v>
+        <v>705</v>
+      </c>
+      <c r="D1322" t="s">
+        <v>80</v>
       </c>
       <c r="E1322" t="s">
-        <v>21</v>
+        <v>26</v>
+      </c>
+      <c r="F1322" t="s">
+        <v>408</v>
+      </c>
+      <c r="G1322" s="1">
+        <v>46787</v>
       </c>
     </row>
     <row r="1323" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1323" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1323" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C1323">
-        <v>3254511340</v>
+        <v>6661044752</v>
       </c>
       <c r="E1323" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1324" spans="1:7" x14ac:dyDescent="0.3">
@@ -30406,7 +30415,7 @@
         <v>3254511340</v>
       </c>
       <c r="E1324" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1325" spans="1:7" x14ac:dyDescent="0.3">
@@ -30419,14 +30428,8 @@
       <c r="C1325">
         <v>3254511340</v>
       </c>
-      <c r="D1325" t="s">
-        <v>18</v>
-      </c>
       <c r="E1325" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1325" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1326" spans="1:7" x14ac:dyDescent="0.3">
@@ -30443,7 +30446,7 @@
         <v>18</v>
       </c>
       <c r="E1326" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F1326" t="s">
         <v>11</v>
@@ -30451,22 +30454,22 @@
     </row>
     <row r="1327" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1327" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B1327" t="s">
-        <v>709</v>
+        <v>8</v>
+      </c>
+      <c r="C1327">
+        <v>3254511340</v>
       </c>
       <c r="D1327" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="E1327" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F1327" t="s">
-        <v>327</v>
-      </c>
-      <c r="G1327" s="1">
-        <v>46823</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1328" spans="1:7" x14ac:dyDescent="0.3">
@@ -30480,13 +30483,13 @@
         <v>58</v>
       </c>
       <c r="E1328" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F1328" t="s">
         <v>327</v>
       </c>
       <c r="G1328" s="1">
-        <v>46824</v>
+        <v>46823</v>
       </c>
     </row>
     <row r="1329" spans="1:7" x14ac:dyDescent="0.3">
@@ -30500,7 +30503,7 @@
         <v>58</v>
       </c>
       <c r="E1329" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F1329" t="s">
         <v>327</v>
@@ -30511,16 +30514,22 @@
     </row>
     <row r="1330" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1330" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B1330" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1330">
-        <v>6230126270</v>
+        <v>709</v>
+      </c>
+      <c r="D1330" t="s">
+        <v>58</v>
       </c>
       <c r="E1330" t="s">
-        <v>10</v>
+        <v>26</v>
+      </c>
+      <c r="F1330" t="s">
+        <v>327</v>
+      </c>
+      <c r="G1330" s="1">
+        <v>46824</v>
       </c>
     </row>
     <row r="1331" spans="1:7" x14ac:dyDescent="0.3">
@@ -30534,7 +30543,7 @@
         <v>6230126270</v>
       </c>
       <c r="E1331" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1332" spans="1:7" x14ac:dyDescent="0.3">
@@ -30547,25 +30556,19 @@
       <c r="C1332">
         <v>6230126270</v>
       </c>
-      <c r="D1332" t="s">
-        <v>18</v>
-      </c>
       <c r="E1332" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1332" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1333" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1333" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B1333" t="s">
         <v>24</v>
       </c>
       <c r="C1333">
-        <v>7725781700</v>
+        <v>6230126270</v>
       </c>
       <c r="D1333" t="s">
         <v>18</v>
@@ -30579,13 +30582,13 @@
     </row>
     <row r="1334" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1334" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B1334" t="s">
         <v>24</v>
       </c>
       <c r="C1334">
-        <v>6453132158</v>
+        <v>7725781700</v>
       </c>
       <c r="D1334" t="s">
         <v>18</v>
@@ -30593,16 +30596,19 @@
       <c r="E1334" t="s">
         <v>19</v>
       </c>
+      <c r="F1334" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1335" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1335" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B1335" t="s">
         <v>24</v>
       </c>
       <c r="C1335">
-        <v>7736365613</v>
+        <v>6453132158</v>
       </c>
       <c r="D1335" t="s">
         <v>18</v>
@@ -30613,25 +30619,19 @@
     </row>
     <row r="1336" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1336" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1336" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="C1336">
-        <v>6321173535</v>
+        <v>7736365613</v>
       </c>
       <c r="D1336" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="E1336" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1336" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1336" s="1">
-        <v>46877</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1337" spans="1:7" x14ac:dyDescent="0.3">
@@ -30645,7 +30645,7 @@
         <v>6321173535</v>
       </c>
       <c r="D1337" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="E1337" t="s">
         <v>10</v>
@@ -30658,17 +30658,26 @@
       </c>
     </row>
     <row r="1338" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1338" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1338" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1338">
+        <v>6321173535</v>
+      </c>
       <c r="D1338" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E1338" t="s">
         <v>10</v>
       </c>
       <c r="F1338" t="s">
-        <v>408</v>
+        <v>11</v>
       </c>
       <c r="G1338" s="1">
-        <v>46857</v>
+        <v>46877</v>
       </c>
     </row>
     <row r="1339" spans="1:7" x14ac:dyDescent="0.3">
@@ -30676,18 +30685,21 @@
         <v>9</v>
       </c>
       <c r="E1339" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F1339" t="s">
         <v>408</v>
       </c>
+      <c r="G1339" s="1">
+        <v>46857</v>
+      </c>
     </row>
     <row r="1340" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D1340" t="s">
         <v>9</v>
       </c>
       <c r="E1340" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F1340" t="s">
         <v>408</v>
@@ -30698,27 +30710,24 @@
         <v>9</v>
       </c>
       <c r="E1341" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F1341" t="s">
         <v>408</v>
       </c>
-      <c r="G1341" s="1">
-        <v>46857</v>
-      </c>
     </row>
     <row r="1342" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D1342" t="s">
         <v>9</v>
       </c>
       <c r="E1342" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F1342" t="s">
         <v>408</v>
       </c>
       <c r="G1342" s="1">
-        <v>46899</v>
+        <v>46857</v>
       </c>
     </row>
     <row r="1343" spans="1:7" x14ac:dyDescent="0.3">
@@ -30726,36 +30735,27 @@
         <v>9</v>
       </c>
       <c r="E1343" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F1343" t="s">
         <v>408</v>
       </c>
       <c r="G1343" s="1">
+        <v>46899</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D1344" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1344" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1344" t="s">
+        <v>408</v>
+      </c>
+      <c r="G1344" s="1">
         <v>46824</v>
-      </c>
-    </row>
-    <row r="1344" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1344" t="s">
-        <v>715</v>
-      </c>
-      <c r="B1344" t="s">
-        <v>716</v>
-      </c>
-      <c r="C1344">
-        <v>6660003190</v>
-      </c>
-      <c r="D1344" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1344" t="s">
-        <v>299</v>
-      </c>
-      <c r="F1344" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1344" s="1">
-        <v>46898</v>
       </c>
     </row>
     <row r="1345" spans="1:7" x14ac:dyDescent="0.3">
@@ -30769,7 +30769,7 @@
         <v>6660003190</v>
       </c>
       <c r="D1345" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E1345" t="s">
         <v>299</v>
@@ -30783,25 +30783,25 @@
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1346" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B1346" t="s">
-        <v>8</v>
+        <v>716</v>
       </c>
       <c r="C1346">
-        <v>1650404549</v>
+        <v>6660003190</v>
       </c>
       <c r="D1346" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="E1346" t="s">
-        <v>10</v>
+        <v>299</v>
       </c>
       <c r="F1346" t="s">
         <v>11</v>
       </c>
       <c r="G1346" s="1">
-        <v>46901</v>
+        <v>46898</v>
       </c>
     </row>
     <row r="1347" spans="1:7" x14ac:dyDescent="0.3">
@@ -30815,7 +30815,7 @@
         <v>1650404549</v>
       </c>
       <c r="D1347" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="E1347" t="s">
         <v>10</v>
@@ -30838,30 +30838,39 @@
         <v>1650404549</v>
       </c>
       <c r="D1348" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E1348" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F1348" t="s">
         <v>11</v>
       </c>
       <c r="G1348" s="1">
-        <v>46902</v>
+        <v>46901</v>
       </c>
     </row>
     <row r="1349" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1349" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B1349" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C1349">
-        <v>1646043628</v>
+        <v>1650404549</v>
+      </c>
+      <c r="D1349" t="s">
+        <v>18</v>
       </c>
       <c r="E1349" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="F1349" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1349" s="1">
+        <v>46902</v>
       </c>
     </row>
     <row r="1350" spans="1:7" x14ac:dyDescent="0.3">
@@ -30875,34 +30884,48 @@
         <v>1646043628</v>
       </c>
       <c r="E1350" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1351" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1351" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B1351" t="s">
         <v>24</v>
       </c>
       <c r="C1351">
-        <v>9710096350</v>
+        <v>1646043628</v>
       </c>
       <c r="E1351" t="s">
-        <v>448</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1352" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1352" t="s">
+        <v>719</v>
+      </c>
+      <c r="B1352" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1352">
+        <v>9710096350</v>
+      </c>
+      <c r="E1352" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1353" t="s">
         <v>720</v>
       </c>
-      <c r="B1352" t="s">
+      <c r="B1353" t="s">
         <v>8</v>
       </c>
-      <c r="C1352">
+      <c r="C1353">
         <v>7810982090</v>
       </c>
-      <c r="E1352" t="s">
+      <c r="E1353" t="s">
         <v>10</v>
       </c>
     </row>
